--- a/Team-Data/2013-14/2-19-2013-14.xlsx
+++ b/Team-Data/2013-14/2-19-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,64 +728,64 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E2" t="n">
         <v>25</v>
       </c>
       <c r="F2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G2" t="n">
-        <v>0.472</v>
+        <v>0.481</v>
       </c>
       <c r="H2" t="n">
         <v>48.5</v>
       </c>
       <c r="I2" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="J2" t="n">
-        <v>82.09999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="K2" t="n">
         <v>0.459</v>
       </c>
       <c r="L2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="N2" t="n">
         <v>0.373</v>
       </c>
       <c r="O2" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="P2" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.778</v>
+        <v>0.777</v>
       </c>
       <c r="R2" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="S2" t="n">
         <v>31.7</v>
       </c>
       <c r="T2" t="n">
-        <v>40.7</v>
+        <v>40.8</v>
       </c>
       <c r="U2" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="V2" t="n">
         <v>15.5</v>
       </c>
       <c r="W2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="X2" t="n">
         <v>4.3</v>
@@ -727,37 +794,37 @@
         <v>4.7</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AB2" t="n">
         <v>101.3</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AF2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AH2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI2" t="n">
         <v>15</v>
       </c>
       <c r="AJ2" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AK2" t="n">
         <v>7</v>
@@ -766,16 +833,16 @@
         <v>4</v>
       </c>
       <c r="AM2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO2" t="n">
         <v>21</v>
       </c>
       <c r="AP2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ2" t="n">
         <v>6</v>
@@ -784,7 +851,7 @@
         <v>27</v>
       </c>
       <c r="AS2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT2" t="n">
         <v>26</v>
@@ -796,25 +863,25 @@
         <v>25</v>
       </c>
       <c r="AW2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ2" t="n">
         <v>4</v>
       </c>
       <c r="BA2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB2" t="n">
         <v>12</v>
       </c>
       <c r="BC2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-19-2013-14</t>
+          <t>2014-02-19</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E3" t="n">
         <v>19</v>
       </c>
       <c r="F3" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G3" t="n">
-        <v>0.345</v>
+        <v>0.352</v>
       </c>
       <c r="H3" t="n">
         <v>48.1</v>
@@ -861,25 +928,25 @@
         <v>36.3</v>
       </c>
       <c r="J3" t="n">
-        <v>83.3</v>
+        <v>83.2</v>
       </c>
       <c r="K3" t="n">
-        <v>0.436</v>
+        <v>0.437</v>
       </c>
       <c r="L3" t="n">
         <v>6.5</v>
       </c>
       <c r="M3" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="N3" t="n">
         <v>0.331</v>
       </c>
       <c r="O3" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="P3" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="Q3" t="n">
         <v>0.766</v>
@@ -894,7 +961,7 @@
         <v>43.1</v>
       </c>
       <c r="U3" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="V3" t="n">
         <v>15.5</v>
@@ -906,22 +973,22 @@
         <v>4.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z3" t="n">
         <v>21.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AB3" t="n">
         <v>95.09999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>-3.6</v>
+        <v>-3.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE3" t="n">
         <v>24</v>
@@ -942,7 +1009,7 @@
         <v>13</v>
       </c>
       <c r="AK3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL3" t="n">
         <v>25</v>
@@ -966,19 +1033,19 @@
         <v>13</v>
       </c>
       <c r="AS3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU3" t="n">
         <v>26</v>
       </c>
       <c r="AV3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW3" t="n">
         <v>23</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>24</v>
       </c>
       <c r="AX3" t="n">
         <v>15</v>
@@ -990,10 +1057,10 @@
         <v>19</v>
       </c>
       <c r="BA3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC3" t="n">
         <v>24</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-19-2013-14</t>
+          <t>2014-02-19</t>
         </is>
       </c>
     </row>
@@ -1025,28 +1092,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F4" t="n">
         <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>0.481</v>
+        <v>0.471</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
       </c>
       <c r="I4" t="n">
-        <v>35.3</v>
+        <v>35.2</v>
       </c>
       <c r="J4" t="n">
         <v>78.3</v>
       </c>
       <c r="K4" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="L4" t="n">
         <v>8</v>
@@ -1055,31 +1122,31 @@
         <v>21.9</v>
       </c>
       <c r="N4" t="n">
-        <v>0.367</v>
+        <v>0.366</v>
       </c>
       <c r="O4" t="n">
         <v>18.7</v>
       </c>
       <c r="P4" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.761</v>
+        <v>0.762</v>
       </c>
       <c r="R4" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="T4" t="n">
-        <v>39</v>
+        <v>39.1</v>
       </c>
       <c r="U4" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="V4" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W4" t="n">
         <v>7.9</v>
@@ -1088,31 +1155,31 @@
         <v>4.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB4" t="n">
-        <v>97.40000000000001</v>
+        <v>97.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2.1</v>
+        <v>-2.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AE4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF4" t="n">
         <v>14</v>
       </c>
       <c r="AG4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH4" t="n">
         <v>7</v>
@@ -1163,13 +1230,13 @@
         <v>12</v>
       </c>
       <c r="AX4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY4" t="n">
         <v>8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA4" t="n">
         <v>11</v>
@@ -1178,7 +1245,7 @@
         <v>21</v>
       </c>
       <c r="BC4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-19-2013-14</t>
+          <t>2014-02-19</t>
         </is>
       </c>
     </row>
@@ -1207,58 +1274,58 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F5" t="n">
         <v>30</v>
       </c>
       <c r="G5" t="n">
-        <v>0.455</v>
+        <v>0.444</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
       </c>
       <c r="I5" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="J5" t="n">
         <v>81.40000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.439</v>
+        <v>0.438</v>
       </c>
       <c r="L5" t="n">
         <v>5.8</v>
       </c>
       <c r="M5" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="N5" t="n">
-        <v>0.355</v>
+        <v>0.354</v>
       </c>
       <c r="O5" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="P5" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.724</v>
+        <v>0.723</v>
       </c>
       <c r="R5" t="n">
         <v>9</v>
       </c>
       <c r="S5" t="n">
-        <v>33.2</v>
+        <v>33.1</v>
       </c>
       <c r="T5" t="n">
-        <v>42.2</v>
+        <v>42</v>
       </c>
       <c r="U5" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="V5" t="n">
         <v>12.6</v>
@@ -1267,7 +1334,7 @@
         <v>6.2</v>
       </c>
       <c r="X5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="n">
         <v>5.4</v>
@@ -1279,19 +1346,19 @@
         <v>21.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>95.3</v>
+        <v>95</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.7</v>
+        <v>-2.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG5" t="n">
         <v>19</v>
@@ -1300,13 +1367,13 @@
         <v>16</v>
       </c>
       <c r="AI5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ5" t="n">
         <v>24</v>
       </c>
       <c r="AK5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AL5" t="n">
         <v>29</v>
@@ -1330,13 +1397,13 @@
         <v>28</v>
       </c>
       <c r="AS5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AV5" t="n">
         <v>1</v>
@@ -1357,7 +1424,7 @@
         <v>10</v>
       </c>
       <c r="BB5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC5" t="n">
         <v>20</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-19-2013-14</t>
+          <t>2014-02-19</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F6" t="n">
         <v>25</v>
       </c>
       <c r="G6" t="n">
-        <v>0.528</v>
+        <v>0.519</v>
       </c>
       <c r="H6" t="n">
         <v>48.8</v>
@@ -1407,25 +1474,25 @@
         <v>34.3</v>
       </c>
       <c r="J6" t="n">
-        <v>80.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.427</v>
+        <v>0.425</v>
       </c>
       <c r="L6" t="n">
         <v>5.9</v>
       </c>
       <c r="M6" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0.338</v>
+        <v>0.335</v>
       </c>
       <c r="O6" t="n">
         <v>17.8</v>
       </c>
       <c r="P6" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="Q6" t="n">
         <v>0.77</v>
@@ -1434,10 +1501,10 @@
         <v>12</v>
       </c>
       <c r="S6" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="T6" t="n">
-        <v>44.7</v>
+        <v>44.8</v>
       </c>
       <c r="U6" t="n">
         <v>22.2</v>
@@ -1455,25 +1522,25 @@
         <v>6.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AB6" t="n">
         <v>92.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
       </c>
       <c r="AF6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG6" t="n">
         <v>13</v>
@@ -1503,16 +1570,16 @@
         <v>14</v>
       </c>
       <c r="AP6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ6" t="n">
         <v>10</v>
       </c>
       <c r="AR6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT6" t="n">
         <v>9</v>
@@ -1521,7 +1588,7 @@
         <v>11</v>
       </c>
       <c r="AV6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW6" t="n">
         <v>20</v>
@@ -1542,7 +1609,7 @@
         <v>30</v>
       </c>
       <c r="BC6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-19-2013-14</t>
+          <t>2014-02-19</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F7" t="n">
         <v>33</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4</v>
+        <v>0.389</v>
       </c>
       <c r="H7" t="n">
         <v>48.8</v>
@@ -1589,7 +1656,7 @@
         <v>36.4</v>
       </c>
       <c r="J7" t="n">
-        <v>85.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="K7" t="n">
         <v>0.425</v>
@@ -1601,58 +1668,58 @@
         <v>19.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0.356</v>
+        <v>0.358</v>
       </c>
       <c r="O7" t="n">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="P7" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.744</v>
+        <v>0.742</v>
       </c>
       <c r="R7" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="S7" t="n">
-        <v>31.8</v>
+        <v>31.6</v>
       </c>
       <c r="T7" t="n">
-        <v>44.5</v>
+        <v>44.4</v>
       </c>
       <c r="U7" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V7" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W7" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X7" t="n">
         <v>3.9</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z7" t="n">
         <v>20.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AB7" t="n">
-        <v>97.09999999999999</v>
+        <v>97</v>
       </c>
       <c r="AC7" t="n">
-        <v>-4.5</v>
+        <v>-4.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF7" t="n">
         <v>22</v>
@@ -1679,13 +1746,13 @@
         <v>21</v>
       </c>
       <c r="AN7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO7" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AP7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ7" t="n">
         <v>22</v>
@@ -1694,10 +1761,10 @@
         <v>3</v>
       </c>
       <c r="AS7" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AT7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU7" t="n">
         <v>27</v>
@@ -1706,7 +1773,7 @@
         <v>11</v>
       </c>
       <c r="AW7" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AX7" t="n">
         <v>29</v>
@@ -1718,7 +1785,7 @@
         <v>14</v>
       </c>
       <c r="BA7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB7" t="n">
         <v>23</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-19-2013-14</t>
+          <t>2014-02-19</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>1.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
         <v>8</v>
@@ -1843,7 +1910,7 @@
         <v>10</v>
       </c>
       <c r="AH8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI8" t="n">
         <v>3</v>
@@ -1855,7 +1922,7 @@
         <v>6</v>
       </c>
       <c r="AL8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM8" t="n">
         <v>11</v>
@@ -1864,7 +1931,7 @@
         <v>6</v>
       </c>
       <c r="AO8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP8" t="n">
         <v>23</v>
@@ -1882,7 +1949,7 @@
         <v>28</v>
       </c>
       <c r="AU8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV8" t="n">
         <v>3</v>
@@ -1897,7 +1964,7 @@
         <v>3</v>
       </c>
       <c r="AZ8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA8" t="n">
         <v>23</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-19-2013-14</t>
+          <t>2014-02-19</t>
         </is>
       </c>
     </row>
@@ -2013,13 +2080,13 @@
         <v>-1.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AE9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AF9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG9" t="n">
         <v>18</v>
@@ -2037,13 +2104,13 @@
         <v>17</v>
       </c>
       <c r="AL9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM9" t="n">
         <v>9</v>
       </c>
       <c r="AN9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO9" t="n">
         <v>7</v>
@@ -2058,7 +2125,7 @@
         <v>5</v>
       </c>
       <c r="AS9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT9" t="n">
         <v>4</v>
@@ -2067,10 +2134,10 @@
         <v>13</v>
       </c>
       <c r="AV9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX9" t="n">
         <v>5</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-19-2013-14</t>
+          <t>2014-02-19</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E10" t="n">
         <v>22</v>
       </c>
       <c r="F10" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G10" t="n">
-        <v>0.407</v>
+        <v>0.415</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
@@ -2135,7 +2202,7 @@
         <v>38.6</v>
       </c>
       <c r="J10" t="n">
-        <v>86.3</v>
+        <v>86.2</v>
       </c>
       <c r="K10" t="n">
         <v>0.448</v>
@@ -2144,55 +2211,55 @@
         <v>6</v>
       </c>
       <c r="M10" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="N10" t="n">
-        <v>0.311</v>
+        <v>0.309</v>
       </c>
       <c r="O10" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="P10" t="n">
-        <v>25.8</v>
+        <v>25.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.666</v>
+        <v>0.665</v>
       </c>
       <c r="R10" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="S10" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="T10" t="n">
-        <v>45.1</v>
+        <v>45.3</v>
       </c>
       <c r="U10" t="n">
         <v>20.5</v>
       </c>
       <c r="V10" t="n">
-        <v>15.2</v>
+        <v>15.4</v>
       </c>
       <c r="W10" t="n">
         <v>8.9</v>
       </c>
       <c r="X10" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z10" t="n">
         <v>20.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>100.4</v>
+        <v>100.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.5</v>
+        <v>-2.2</v>
       </c>
       <c r="AD10" t="n">
         <v>10</v>
@@ -2228,7 +2295,7 @@
         <v>30</v>
       </c>
       <c r="AO10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP10" t="n">
         <v>6</v>
@@ -2243,13 +2310,13 @@
         <v>24</v>
       </c>
       <c r="AT10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU10" t="n">
         <v>23</v>
       </c>
       <c r="AV10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AW10" t="n">
         <v>3</v>
@@ -2258,7 +2325,7 @@
         <v>9</v>
       </c>
       <c r="AY10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ10" t="n">
         <v>15</v>
@@ -2267,10 +2334,10 @@
         <v>13</v>
       </c>
       <c r="BB10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC10" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-19-2013-14</t>
+          <t>2014-02-19</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E11" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F11" t="n">
         <v>22</v>
       </c>
       <c r="G11" t="n">
-        <v>0.593</v>
+        <v>0.585</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
@@ -2323,43 +2390,43 @@
         <v>0.459</v>
       </c>
       <c r="L11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="N11" t="n">
-        <v>0.381</v>
+        <v>0.384</v>
       </c>
       <c r="O11" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="P11" t="n">
         <v>22</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.743</v>
+        <v>0.741</v>
       </c>
       <c r="R11" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="S11" t="n">
-        <v>34.6</v>
+        <v>34.7</v>
       </c>
       <c r="T11" t="n">
-        <v>45.8</v>
+        <v>46</v>
       </c>
       <c r="U11" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="V11" t="n">
-        <v>15.9</v>
+        <v>16.1</v>
       </c>
       <c r="W11" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="X11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y11" t="n">
         <v>4.4</v>
@@ -2371,16 +2438,16 @@
         <v>19.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>103.5</v>
+        <v>103.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AD11" t="n">
         <v>10</v>
       </c>
       <c r="AE11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF11" t="n">
         <v>9</v>
@@ -2401,16 +2468,16 @@
         <v>8</v>
       </c>
       <c r="AL11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AM11" t="n">
         <v>7</v>
       </c>
       <c r="AN11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AO11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP11" t="n">
         <v>20</v>
@@ -2434,10 +2501,10 @@
         <v>28</v>
       </c>
       <c r="AW11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-19-2013-14</t>
+          <t>2014-02-19</t>
         </is>
       </c>
     </row>
@@ -2481,64 +2548,64 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E12" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F12" t="n">
         <v>17</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.679</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
       </c>
       <c r="I12" t="n">
-        <v>37.6</v>
+        <v>37.4</v>
       </c>
       <c r="J12" t="n">
-        <v>79.3</v>
+        <v>78.8</v>
       </c>
       <c r="K12" t="n">
-        <v>0.475</v>
+        <v>0.474</v>
       </c>
       <c r="L12" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="M12" t="n">
-        <v>26</v>
+        <v>25.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0.354</v>
+        <v>0.35</v>
       </c>
       <c r="O12" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="P12" t="n">
-        <v>31.2</v>
+        <v>31.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="R12" t="n">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
       <c r="S12" t="n">
         <v>34</v>
       </c>
       <c r="T12" t="n">
-        <v>45.1</v>
+        <v>44.9</v>
       </c>
       <c r="U12" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V12" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="W12" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X12" t="n">
         <v>5.8</v>
@@ -2547,22 +2614,22 @@
         <v>5.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>106</v>
+        <v>105.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AD12" t="n">
         <v>10</v>
       </c>
       <c r="AE12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF12" t="n">
         <v>5</v>
@@ -2583,16 +2650,16 @@
         <v>4</v>
       </c>
       <c r="AL12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM12" t="n">
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AO12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP12" t="n">
         <v>1</v>
@@ -2601,22 +2668,22 @@
         <v>29</v>
       </c>
       <c r="AR12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AS12" t="n">
         <v>4</v>
       </c>
       <c r="AT12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AV12" t="n">
         <v>29</v>
       </c>
       <c r="AW12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AX12" t="n">
         <v>3</v>
@@ -2625,7 +2692,7 @@
         <v>23</v>
       </c>
       <c r="AZ12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA12" t="n">
         <v>1</v>
@@ -2634,7 +2701,7 @@
         <v>3</v>
       </c>
       <c r="BC12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-19-2013-14</t>
+          <t>2014-02-19</t>
         </is>
       </c>
     </row>
@@ -2663,82 +2730,82 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E13" t="n">
         <v>41</v>
       </c>
       <c r="F13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G13" t="n">
-        <v>0.759</v>
+        <v>0.774</v>
       </c>
       <c r="H13" t="n">
         <v>48.3</v>
       </c>
       <c r="I13" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="J13" t="n">
-        <v>81.09999999999999</v>
+        <v>81</v>
       </c>
       <c r="K13" t="n">
-        <v>0.453</v>
+        <v>0.454</v>
       </c>
       <c r="L13" t="n">
         <v>6.9</v>
       </c>
       <c r="M13" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0.35</v>
+        <v>0.352</v>
       </c>
       <c r="O13" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="P13" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.781</v>
+        <v>0.782</v>
       </c>
       <c r="R13" t="n">
         <v>10.2</v>
       </c>
       <c r="S13" t="n">
-        <v>35.3</v>
+        <v>35.2</v>
       </c>
       <c r="T13" t="n">
-        <v>45.5</v>
+        <v>45.4</v>
       </c>
       <c r="U13" t="n">
         <v>20.5</v>
       </c>
       <c r="V13" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="W13" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X13" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Y13" t="n">
         <v>4.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>98.59999999999999</v>
+        <v>98.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD13" t="n">
         <v>10</v>
@@ -2747,7 +2814,7 @@
         <v>2</v>
       </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG13" t="n">
         <v>2</v>
@@ -2771,7 +2838,7 @@
         <v>22</v>
       </c>
       <c r="AN13" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO13" t="n">
         <v>11</v>
@@ -2780,7 +2847,7 @@
         <v>13</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR13" t="n">
         <v>22</v>
@@ -2789,16 +2856,16 @@
         <v>1</v>
       </c>
       <c r="AT13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AU13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW13" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AX13" t="n">
         <v>4</v>
@@ -2807,7 +2874,7 @@
         <v>11</v>
       </c>
       <c r="AZ13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA13" t="n">
         <v>6</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-19-2013-14</t>
+          <t>2014-02-19</t>
         </is>
       </c>
     </row>
@@ -2947,16 +3014,16 @@
         <v>5</v>
       </c>
       <c r="AL14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM14" t="n">
         <v>8</v>
       </c>
       <c r="AN14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP14" t="n">
         <v>2</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-19-2013-14</t>
+          <t>2014-02-19</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E15" t="n">
         <v>18</v>
       </c>
       <c r="F15" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G15" t="n">
-        <v>0.333</v>
+        <v>0.34</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
@@ -3048,7 +3115,7 @@
         <v>84</v>
       </c>
       <c r="K15" t="n">
-        <v>0.443</v>
+        <v>0.442</v>
       </c>
       <c r="L15" t="n">
         <v>9.199999999999999</v>
@@ -3057,34 +3124,34 @@
         <v>24.7</v>
       </c>
       <c r="N15" t="n">
-        <v>0.374</v>
+        <v>0.371</v>
       </c>
       <c r="O15" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="P15" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="R15" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="S15" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="T15" t="n">
-        <v>42.2</v>
+        <v>42.4</v>
       </c>
       <c r="U15" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="V15" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="W15" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="X15" t="n">
         <v>5.5</v>
@@ -3099,10 +3166,10 @@
         <v>19.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>100.6</v>
+        <v>100.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.6</v>
+        <v>-5.2</v>
       </c>
       <c r="AD15" t="n">
         <v>10</v>
@@ -3129,13 +3196,13 @@
         <v>20</v>
       </c>
       <c r="AL15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AM15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO15" t="n">
         <v>19</v>
@@ -3150,16 +3217,16 @@
         <v>24</v>
       </c>
       <c r="AS15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW15" t="n">
         <v>28</v>
@@ -3174,13 +3241,13 @@
         <v>10</v>
       </c>
       <c r="BA15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-19-2013-14</t>
+          <t>2014-02-19</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>0.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="AE16" t="n">
         <v>11</v>
@@ -3299,7 +3366,7 @@
         <v>11</v>
       </c>
       <c r="AH16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI16" t="n">
         <v>17</v>
@@ -3326,7 +3393,7 @@
         <v>28</v>
       </c>
       <c r="AQ16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR16" t="n">
         <v>11</v>
@@ -3338,7 +3405,7 @@
         <v>18</v>
       </c>
       <c r="AU16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV16" t="n">
         <v>4</v>
@@ -3347,7 +3414,7 @@
         <v>16</v>
       </c>
       <c r="AX16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY16" t="n">
         <v>21</v>
@@ -3356,13 +3423,13 @@
         <v>7</v>
       </c>
       <c r="BA16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BB16" t="n">
         <v>27</v>
       </c>
       <c r="BC16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-19-2013-14</t>
+          <t>2014-02-19</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>5.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AE17" t="n">
         <v>4</v>
@@ -3481,7 +3548,7 @@
         <v>3</v>
       </c>
       <c r="AH17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI17" t="n">
         <v>5</v>
@@ -3496,10 +3563,10 @@
         <v>11</v>
       </c>
       <c r="AM17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO17" t="n">
         <v>12</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-19-2013-14</t>
+          <t>2014-02-19</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3678,10 +3745,10 @@
         <v>18</v>
       </c>
       <c r="AM18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO18" t="n">
         <v>28</v>
@@ -3696,19 +3763,19 @@
         <v>14</v>
       </c>
       <c r="AS18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT18" t="n">
         <v>25</v>
       </c>
       <c r="AU18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV18" t="n">
         <v>22</v>
       </c>
       <c r="AW18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX18" t="n">
         <v>7</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-19-2013-14</t>
+          <t>2014-02-19</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F19" t="n">
         <v>28</v>
       </c>
       <c r="G19" t="n">
-        <v>0.481</v>
+        <v>0.472</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
@@ -3773,34 +3840,34 @@
         <v>38.4</v>
       </c>
       <c r="J19" t="n">
-        <v>87.90000000000001</v>
+        <v>88</v>
       </c>
       <c r="K19" t="n">
-        <v>0.437</v>
+        <v>0.436</v>
       </c>
       <c r="L19" t="n">
         <v>7.5</v>
       </c>
       <c r="M19" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="N19" t="n">
         <v>0.343</v>
       </c>
       <c r="O19" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="P19" t="n">
-        <v>27.1</v>
+        <v>27</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.78</v>
+        <v>0.784</v>
       </c>
       <c r="R19" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="S19" t="n">
-        <v>33</v>
+        <v>32.9</v>
       </c>
       <c r="T19" t="n">
         <v>45.7</v>
@@ -3812,25 +3879,25 @@
         <v>13.8</v>
       </c>
       <c r="W19" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X19" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="AB19" t="n">
         <v>105.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AD19" t="n">
         <v>10</v>
@@ -3839,10 +3906,10 @@
         <v>14</v>
       </c>
       <c r="AF19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG19" t="n">
         <v>15</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>14</v>
       </c>
       <c r="AH19" t="n">
         <v>25</v>
@@ -3851,16 +3918,16 @@
         <v>10</v>
       </c>
       <c r="AJ19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL19" t="n">
         <v>16</v>
       </c>
       <c r="AM19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN19" t="n">
         <v>26</v>
@@ -3872,13 +3939,13 @@
         <v>3</v>
       </c>
       <c r="AQ19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AS19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT19" t="n">
         <v>3</v>
@@ -3890,7 +3957,7 @@
         <v>7</v>
       </c>
       <c r="AW19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX19" t="n">
         <v>30</v>
@@ -3905,7 +3972,7 @@
         <v>3</v>
       </c>
       <c r="BB19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC19" t="n">
         <v>9</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-19-2013-14</t>
+          <t>2014-02-19</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E20" t="n">
         <v>23</v>
       </c>
       <c r="F20" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G20" t="n">
-        <v>0.434</v>
+        <v>0.442</v>
       </c>
       <c r="H20" t="n">
         <v>48.4</v>
@@ -3955,7 +4022,7 @@
         <v>38.1</v>
       </c>
       <c r="J20" t="n">
-        <v>83.40000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K20" t="n">
         <v>0.456</v>
@@ -3964,19 +4031,19 @@
         <v>6</v>
       </c>
       <c r="M20" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="N20" t="n">
-        <v>0.382</v>
+        <v>0.384</v>
       </c>
       <c r="O20" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="P20" t="n">
         <v>22.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.764</v>
+        <v>0.765</v>
       </c>
       <c r="R20" t="n">
         <v>12.2</v>
@@ -3988,7 +4055,7 @@
         <v>42.5</v>
       </c>
       <c r="U20" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="V20" t="n">
         <v>13.8</v>
@@ -3997,7 +4064,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="X20" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="Y20" t="n">
         <v>6</v>
@@ -4006,16 +4073,16 @@
         <v>22.6</v>
       </c>
       <c r="AA20" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>99.5</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="AC20" t="n">
-        <v>-1.7</v>
+        <v>-1.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE20" t="n">
         <v>20</v>
@@ -4030,7 +4097,7 @@
         <v>13</v>
       </c>
       <c r="AI20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ20" t="n">
         <v>11</v>
@@ -4045,7 +4112,7 @@
         <v>29</v>
       </c>
       <c r="AN20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO20" t="n">
         <v>15</v>
@@ -4066,10 +4133,10 @@
         <v>17</v>
       </c>
       <c r="AU20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW20" t="n">
         <v>10</v>
@@ -4087,7 +4154,7 @@
         <v>21</v>
       </c>
       <c r="BB20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC20" t="n">
         <v>18</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-19-2013-14</t>
+          <t>2014-02-19</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F21" t="n">
         <v>33</v>
       </c>
       <c r="G21" t="n">
-        <v>0.389</v>
+        <v>0.377</v>
       </c>
       <c r="H21" t="n">
         <v>48.5</v>
@@ -4149,7 +4216,7 @@
         <v>24.3</v>
       </c>
       <c r="N21" t="n">
-        <v>0.366</v>
+        <v>0.364</v>
       </c>
       <c r="O21" t="n">
         <v>14.8</v>
@@ -4158,22 +4225,22 @@
         <v>19.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.749</v>
+        <v>0.75</v>
       </c>
       <c r="R21" t="n">
         <v>10.9</v>
       </c>
       <c r="S21" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T21" t="n">
-        <v>40.6</v>
+        <v>40.7</v>
       </c>
       <c r="U21" t="n">
         <v>20.4</v>
       </c>
       <c r="V21" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="W21" t="n">
         <v>7.8</v>
@@ -4182,10 +4249,10 @@
         <v>4.6</v>
       </c>
       <c r="Y21" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Z21" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AA21" t="n">
         <v>19.7</v>
@@ -4194,7 +4261,7 @@
         <v>97.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>-1.7</v>
+        <v>-1.9</v>
       </c>
       <c r="AD21" t="n">
         <v>10</v>
@@ -4227,7 +4294,7 @@
         <v>6</v>
       </c>
       <c r="AN21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO21" t="n">
         <v>30</v>
@@ -4236,13 +4303,13 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR21" t="n">
         <v>19</v>
       </c>
       <c r="AS21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT21" t="n">
         <v>27</v>
@@ -4254,10 +4321,10 @@
         <v>2</v>
       </c>
       <c r="AW21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY21" t="n">
         <v>4</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-19-2013-14</t>
+          <t>2014-02-19</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>7.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4397,7 +4464,7 @@
         <v>4</v>
       </c>
       <c r="AJ22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK22" t="n">
         <v>3</v>
@@ -4421,19 +4488,19 @@
         <v>2</v>
       </c>
       <c r="AR22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS22" t="n">
         <v>3</v>
       </c>
       <c r="AT22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU22" t="n">
         <v>14</v>
       </c>
       <c r="AV22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW22" t="n">
         <v>11</v>
@@ -4448,10 +4515,10 @@
         <v>21</v>
       </c>
       <c r="BA22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-19-2013-14</t>
+          <t>2014-02-19</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E23" t="n">
         <v>16</v>
       </c>
       <c r="F23" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G23" t="n">
-        <v>0.286</v>
+        <v>0.291</v>
       </c>
       <c r="H23" t="n">
         <v>48.6</v>
@@ -4501,34 +4568,34 @@
         <v>36.3</v>
       </c>
       <c r="J23" t="n">
-        <v>82.3</v>
+        <v>82.2</v>
       </c>
       <c r="K23" t="n">
-        <v>0.441</v>
+        <v>0.442</v>
       </c>
       <c r="L23" t="n">
         <v>7</v>
       </c>
       <c r="M23" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="N23" t="n">
-        <v>0.349</v>
+        <v>0.351</v>
       </c>
       <c r="O23" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="P23" t="n">
         <v>21.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.76</v>
+        <v>0.761</v>
       </c>
       <c r="R23" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>32.8</v>
+        <v>32.7</v>
       </c>
       <c r="T23" t="n">
         <v>42.1</v>
@@ -4537,7 +4604,7 @@
         <v>20.6</v>
       </c>
       <c r="V23" t="n">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="W23" t="n">
         <v>7.6</v>
@@ -4549,19 +4616,19 @@
         <v>5.9</v>
       </c>
       <c r="Z23" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AA23" t="n">
         <v>18.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>96</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.4</v>
+        <v>-5.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE23" t="n">
         <v>28</v>
@@ -4573,13 +4640,13 @@
         <v>28</v>
       </c>
       <c r="AH23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI23" t="n">
         <v>23</v>
       </c>
       <c r="AJ23" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AK23" t="n">
         <v>21</v>
@@ -4591,7 +4658,7 @@
         <v>20</v>
       </c>
       <c r="AN23" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AO23" t="n">
         <v>22</v>
@@ -4606,22 +4673,22 @@
         <v>25</v>
       </c>
       <c r="AS23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU23" t="n">
         <v>21</v>
       </c>
       <c r="AV23" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AW23" t="n">
         <v>15</v>
       </c>
       <c r="AX23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY23" t="n">
         <v>26</v>
@@ -4636,7 +4703,7 @@
         <v>24</v>
       </c>
       <c r="BC23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-19-2013-14</t>
+          <t>2014-02-19</t>
         </is>
       </c>
     </row>
@@ -4743,19 +4810,19 @@
         <v>-10.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE24" t="n">
         <v>29</v>
       </c>
       <c r="AF24" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG24" t="n">
         <v>29</v>
       </c>
       <c r="AH24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI24" t="n">
         <v>11</v>
@@ -4779,7 +4846,7 @@
         <v>20</v>
       </c>
       <c r="AP24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ24" t="n">
         <v>28</v>
@@ -4812,7 +4879,7 @@
         <v>22</v>
       </c>
       <c r="BA24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB24" t="n">
         <v>16</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-19-2013-14</t>
+          <t>2014-02-19</t>
         </is>
       </c>
     </row>
@@ -4847,37 +4914,37 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E25" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F25" t="n">
         <v>21</v>
       </c>
       <c r="G25" t="n">
-        <v>0.604</v>
+        <v>0.596</v>
       </c>
       <c r="H25" t="n">
         <v>48.3</v>
       </c>
       <c r="I25" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="J25" t="n">
-        <v>84.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K25" t="n">
         <v>0.457</v>
       </c>
       <c r="L25" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="M25" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="N25" t="n">
-        <v>0.371</v>
+        <v>0.37</v>
       </c>
       <c r="O25" t="n">
         <v>18.5</v>
@@ -4886,7 +4953,7 @@
         <v>24.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.763</v>
+        <v>0.765</v>
       </c>
       <c r="R25" t="n">
         <v>11.6</v>
@@ -4898,10 +4965,10 @@
         <v>43.6</v>
       </c>
       <c r="U25" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="V25" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W25" t="n">
         <v>8.300000000000001</v>
@@ -4916,19 +4983,19 @@
         <v>22.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>105</v>
+        <v>105.1</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF25" t="n">
         <v>8</v>
@@ -4955,7 +5022,7 @@
         <v>2</v>
       </c>
       <c r="AN25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO25" t="n">
         <v>10</v>
@@ -4991,13 +5058,13 @@
         <v>9</v>
       </c>
       <c r="AZ25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA25" t="n">
         <v>8</v>
       </c>
       <c r="BB25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-19-2013-14</t>
+          <t>2014-02-19</t>
         </is>
       </c>
     </row>
@@ -5029,25 +5096,25 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E26" t="n">
         <v>36</v>
       </c>
       <c r="F26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G26" t="n">
-        <v>0.667</v>
+        <v>0.679</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>39.8</v>
+        <v>39.7</v>
       </c>
       <c r="J26" t="n">
-        <v>88.09999999999999</v>
+        <v>88</v>
       </c>
       <c r="K26" t="n">
         <v>0.452</v>
@@ -5056,19 +5123,19 @@
         <v>9.4</v>
       </c>
       <c r="M26" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="N26" t="n">
-        <v>0.38</v>
+        <v>0.381</v>
       </c>
       <c r="O26" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="P26" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="R26" t="n">
         <v>12.8</v>
@@ -5077,16 +5144,16 @@
         <v>33.4</v>
       </c>
       <c r="T26" t="n">
-        <v>46.1</v>
+        <v>46.2</v>
       </c>
       <c r="U26" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="V26" t="n">
         <v>13.8</v>
       </c>
       <c r="W26" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="X26" t="n">
         <v>4.7</v>
@@ -5104,22 +5171,22 @@
         <v>107.9</v>
       </c>
       <c r="AC26" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AD26" t="n">
         <v>10</v>
       </c>
       <c r="AE26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI26" t="n">
         <v>2</v>
@@ -5137,19 +5204,19 @@
         <v>5</v>
       </c>
       <c r="AN26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO26" t="n">
         <v>6</v>
       </c>
       <c r="AP26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ26" t="n">
         <v>1</v>
       </c>
       <c r="AR26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AS26" t="n">
         <v>6</v>
@@ -5161,7 +5228,7 @@
         <v>4</v>
       </c>
       <c r="AV26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW26" t="n">
         <v>30</v>
@@ -5170,7 +5237,7 @@
         <v>16</v>
       </c>
       <c r="AY26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ26" t="n">
         <v>6</v>
@@ -5182,7 +5249,7 @@
         <v>1</v>
       </c>
       <c r="BC26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-19-2013-14</t>
+          <t>2014-02-19</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E27" t="n">
         <v>18</v>
       </c>
       <c r="F27" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G27" t="n">
-        <v>0.333</v>
+        <v>0.34</v>
       </c>
       <c r="H27" t="n">
         <v>48.5</v>
@@ -5229,7 +5296,7 @@
         <v>37.1</v>
       </c>
       <c r="J27" t="n">
-        <v>83.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="K27" t="n">
         <v>0.446</v>
@@ -5238,10 +5305,10 @@
         <v>6.7</v>
       </c>
       <c r="M27" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="N27" t="n">
-        <v>0.344</v>
+        <v>0.343</v>
       </c>
       <c r="O27" t="n">
         <v>20.3</v>
@@ -5250,43 +5317,43 @@
         <v>26.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.775</v>
+        <v>0.776</v>
       </c>
       <c r="R27" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="S27" t="n">
         <v>31.7</v>
       </c>
       <c r="T27" t="n">
-        <v>43.8</v>
+        <v>43.7</v>
       </c>
       <c r="U27" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="V27" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="W27" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X27" t="n">
         <v>4</v>
       </c>
       <c r="Y27" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Z27" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AA27" t="n">
         <v>22.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>101.1</v>
+        <v>101.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>-2.4</v>
+        <v>-2.3</v>
       </c>
       <c r="AD27" t="n">
         <v>10</v>
@@ -5313,13 +5380,13 @@
         <v>18</v>
       </c>
       <c r="AL27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM27" t="n">
         <v>24</v>
       </c>
       <c r="AN27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO27" t="n">
         <v>4</v>
@@ -5328,13 +5395,13 @@
         <v>4</v>
       </c>
       <c r="AQ27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR27" t="n">
         <v>8</v>
       </c>
-      <c r="AR27" t="n">
-        <v>7</v>
-      </c>
       <c r="AS27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT27" t="n">
         <v>12</v>
@@ -5343,7 +5410,7 @@
         <v>29</v>
       </c>
       <c r="AV27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW27" t="n">
         <v>21</v>
@@ -5364,7 +5431,7 @@
         <v>13</v>
       </c>
       <c r="BC27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-19-2013-14</t>
+          <t>2014-02-19</t>
         </is>
       </c>
     </row>
@@ -5393,43 +5460,43 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E28" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F28" t="n">
         <v>15</v>
       </c>
       <c r="G28" t="n">
-        <v>0.727</v>
+        <v>0.722</v>
       </c>
       <c r="H28" t="n">
         <v>48.3</v>
       </c>
       <c r="I28" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="J28" t="n">
-        <v>82.3</v>
+        <v>82.2</v>
       </c>
       <c r="K28" t="n">
         <v>0.49</v>
       </c>
       <c r="L28" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="M28" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="N28" t="n">
-        <v>0.393</v>
+        <v>0.394</v>
       </c>
       <c r="O28" t="n">
         <v>15.3</v>
       </c>
       <c r="P28" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="Q28" t="n">
         <v>0.775</v>
@@ -5438,13 +5505,13 @@
         <v>8.9</v>
       </c>
       <c r="S28" t="n">
-        <v>33.4</v>
+        <v>33.5</v>
       </c>
       <c r="T28" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="U28" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="V28" t="n">
         <v>14.7</v>
@@ -5459,19 +5526,19 @@
         <v>4.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="AA28" t="n">
         <v>19.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>104.1</v>
+        <v>104</v>
       </c>
       <c r="AC28" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE28" t="n">
         <v>3</v>
@@ -5489,13 +5556,13 @@
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
       </c>
       <c r="AL28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM28" t="n">
         <v>19</v>
@@ -5510,7 +5577,7 @@
         <v>29</v>
       </c>
       <c r="AQ28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR28" t="n">
         <v>29</v>
@@ -5528,10 +5595,10 @@
         <v>13</v>
       </c>
       <c r="AW28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY28" t="n">
         <v>18</v>
@@ -5540,7 +5607,7 @@
         <v>2</v>
       </c>
       <c r="BA28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB28" t="n">
         <v>8</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-19-2013-14</t>
+          <t>2014-02-19</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E29" t="n">
         <v>29</v>
       </c>
       <c r="F29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G29" t="n">
-        <v>0.537</v>
+        <v>0.547</v>
       </c>
       <c r="H29" t="n">
         <v>48.5</v>
@@ -5599,34 +5666,34 @@
         <v>0.439</v>
       </c>
       <c r="L29" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="M29" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="N29" t="n">
-        <v>0.362</v>
+        <v>0.365</v>
       </c>
       <c r="O29" t="n">
         <v>18.9</v>
       </c>
       <c r="P29" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.774</v>
+        <v>0.773</v>
       </c>
       <c r="R29" t="n">
         <v>11.9</v>
       </c>
       <c r="S29" t="n">
-        <v>31</v>
+        <v>31.2</v>
       </c>
       <c r="T29" t="n">
-        <v>42.9</v>
+        <v>43.1</v>
       </c>
       <c r="U29" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V29" t="n">
         <v>14</v>
@@ -5638,7 +5705,7 @@
         <v>4.3</v>
       </c>
       <c r="Y29" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z29" t="n">
         <v>22.7</v>
@@ -5647,10 +5714,10 @@
         <v>21.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>99.59999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AD29" t="n">
         <v>10</v>
@@ -5674,16 +5741,16 @@
         <v>17</v>
       </c>
       <c r="AK29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AM29" t="n">
         <v>10</v>
       </c>
       <c r="AN29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO29" t="n">
         <v>8</v>
@@ -5701,10 +5768,10 @@
         <v>21</v>
       </c>
       <c r="AT29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV29" t="n">
         <v>9</v>
@@ -5713,7 +5780,7 @@
         <v>25</v>
       </c>
       <c r="AX29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY29" t="n">
         <v>13</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-19-2013-14</t>
+          <t>2014-02-19</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E30" t="n">
         <v>19</v>
       </c>
       <c r="F30" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G30" t="n">
-        <v>0.358</v>
+        <v>0.365</v>
       </c>
       <c r="H30" t="n">
         <v>48.2</v>
@@ -5784,28 +5851,28 @@
         <v>6.7</v>
       </c>
       <c r="M30" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="N30" t="n">
-        <v>0.351</v>
+        <v>0.35</v>
       </c>
       <c r="O30" t="n">
         <v>16.3</v>
       </c>
       <c r="P30" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.752</v>
+        <v>0.749</v>
       </c>
       <c r="R30" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="S30" t="n">
         <v>30.8</v>
       </c>
       <c r="T30" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="U30" t="n">
         <v>20</v>
@@ -5814,34 +5881,34 @@
         <v>14.7</v>
       </c>
       <c r="W30" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="X30" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y30" t="n">
         <v>4.8</v>
       </c>
       <c r="Z30" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AA30" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>94.40000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="AC30" t="n">
         <v>-5.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE30" t="n">
         <v>24</v>
       </c>
       <c r="AF30" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG30" t="n">
         <v>24</v>
@@ -5850,37 +5917,37 @@
         <v>24</v>
       </c>
       <c r="AI30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ30" t="n">
         <v>25</v>
       </c>
       <c r="AK30" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL30" t="n">
         <v>24</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>23</v>
       </c>
       <c r="AM30" t="n">
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP30" t="n">
         <v>21</v>
       </c>
       <c r="AQ30" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AR30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT30" t="n">
         <v>24</v>
@@ -5889,13 +5956,13 @@
         <v>28</v>
       </c>
       <c r="AV30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AW30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY30" t="n">
         <v>17</v>
@@ -5904,7 +5971,7 @@
         <v>18</v>
       </c>
       <c r="BA30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB30" t="n">
         <v>28</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-19-2013-14</t>
+          <t>2014-02-19</t>
         </is>
       </c>
     </row>
@@ -5939,61 +6006,61 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F31" t="n">
         <v>28</v>
       </c>
       <c r="G31" t="n">
-        <v>0.481</v>
+        <v>0.472</v>
       </c>
       <c r="H31" t="n">
         <v>48.8</v>
       </c>
       <c r="I31" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="J31" t="n">
-        <v>84.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="L31" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="M31" t="n">
         <v>20.6</v>
       </c>
       <c r="N31" t="n">
-        <v>0.382</v>
+        <v>0.378</v>
       </c>
       <c r="O31" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="P31" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="Q31" t="n">
         <v>0.728</v>
       </c>
       <c r="R31" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S31" t="n">
         <v>31.5</v>
       </c>
       <c r="T31" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="U31" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="V31" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W31" t="n">
         <v>8.699999999999999</v>
@@ -6002,19 +6069,19 @@
         <v>4.8</v>
       </c>
       <c r="Y31" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AB31" t="n">
-        <v>99.5</v>
+        <v>99.2</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="AD31" t="n">
         <v>10</v>
@@ -6023,16 +6090,16 @@
         <v>14</v>
       </c>
       <c r="AF31" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG31" t="n">
         <v>15</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>14</v>
       </c>
       <c r="AH31" t="n">
         <v>1</v>
       </c>
       <c r="AI31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ31" t="n">
         <v>8</v>
@@ -6047,13 +6114,13 @@
         <v>16</v>
       </c>
       <c r="AN31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AO31" t="n">
         <v>26</v>
       </c>
       <c r="AP31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ31" t="n">
         <v>25</v>
@@ -6086,13 +6153,13 @@
         <v>16</v>
       </c>
       <c r="BA31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-19-2013-14</t>
+          <t>2014-02-19</t>
         </is>
       </c>
     </row>
